--- a/data/publications/handbook-statistics-on-indian-economy/annual-series/output-and-prices/Index Numbers of Infrastructure Industries.xlsx
+++ b/data/publications/handbook-statistics-on-indian-economy/annual-series/output-and-prices/Index Numbers of Infrastructure Industries.xlsx
@@ -8,7 +8,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="52">
   <si>
     <t>Year</t>
   </si>
@@ -43,6 +43,9 @@
     <t>Weight</t>
   </si>
   <si>
+    <t xml:space="preserve">2025-26   </t>
+  </si>
+  <si>
     <t xml:space="preserve">2024-25   </t>
   </si>
   <si>
@@ -160,11 +163,11 @@
     <t>Base Year :  1993-94 = 100</t>
   </si>
   <si>
-    <t xml:space="preserve">Notes :  1. Weights represent weight of Index Number of Industrial Production.
-             2. Refinery Products has 93 per cent of the crude throughout
-             3. Refinery Products’ yearly growth rate of 2012-13 is not comparable with other years on account of inclusion of RIL
-                (SEZ) production data since April, 2012
-Also see Notes on Tables.
+    <t xml:space="preserve">Notes   : 1. Weights represent weight of Index Number of Industrial Production.
+               2. Refinery Products has 93 per cent of the crude throughout.
+               3. Refinery Products’ yearly growth rate of 2012-13 is not comparable with other years on account of inclusion of RIL (SEZ) production 
+                  data since April, 2012
+                  Also see Notes on Tables.
 Source : Ministry of Commerce and Industry, Government of India for base 1993-94 = 100, base 2004-05 = 100 and base 2011-12 = 100.
 </t>
   </si>
@@ -362,7 +365,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="bottom"/>
@@ -397,6 +400,9 @@
     <xf numFmtId="49" fontId="3" fillId="4" borderId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="174" fontId="1" fillId="2" borderId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="174" fontId="1" fillId="4" borderId="6" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -418,36 +424,37 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K57"/>
+  <dimension ref="A1:L59"/>
   <cols>
     <col min="1" max="1" width="4.67767866666667" customWidth="1"/>
     <col min="2" max="2" width="10.9825" customWidth="1"/>
     <col min="3" max="11" width="12.2754066666667" customWidth="1"/>
     <col min="12" max="12" width="11.4654386666667" customWidth="1"/>
+    <col min="13" max="13" width="4.67767866666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="28.7982" customHeight="1"/>
     <row r="2" s="1" customFormat="1" ht="18.6655" customHeight="1">
-      <c r="B2" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
+      <c r="B2" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
     </row>
     <row r="3" s="1" customFormat="1" ht="9.0661" customHeight="1"/>
     <row r="4" s="1" customFormat="1" ht="14.3991" customHeight="1">
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
     </row>
     <row r="5" s="1" customFormat="1" ht="12.7992" customHeight="1">
-      <c r="B5" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="C5" s="15"/>
-      <c r="D5" s="15"/>
+      <c r="B5" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
     </row>
     <row r="6" s="1" customFormat="1" ht="39.9975" customHeight="1">
       <c r="B6" s="2" t="s">
@@ -550,31 +557,31 @@
         <v>11</v>
       </c>
       <c r="C9" s="9">
-        <v>164.9</v>
+        <v>169.4</v>
       </c>
       <c r="D9" s="9">
-        <v>208.6</v>
+        <v>210.7</v>
       </c>
       <c r="E9" s="9">
-        <v>192</v>
+        <v>191.1</v>
       </c>
       <c r="F9" s="9">
-        <v>214.1</v>
+        <v>234.5</v>
       </c>
       <c r="G9" s="9">
-        <v>197.4</v>
+        <v>214.6</v>
       </c>
       <c r="H9" s="9">
-        <v>75.4</v>
+        <v>73.3</v>
       </c>
       <c r="I9" s="9">
-        <v>139.7</v>
+        <v>139.6</v>
       </c>
       <c r="J9" s="9">
-        <v>75.9</v>
+        <v>73.8</v>
       </c>
       <c r="K9" s="9">
-        <v>133.5</v>
+        <v>133.4</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" ht="14.9324" customHeight="1">
@@ -582,31 +589,31 @@
         <v>12</v>
       </c>
       <c r="C10" s="10">
-        <v>157.8</v>
+        <v>164.9</v>
       </c>
       <c r="D10" s="10">
-        <v>198.3</v>
+        <v>208.6</v>
       </c>
       <c r="E10" s="10">
-        <v>182.7</v>
+        <v>192</v>
       </c>
       <c r="F10" s="10">
-        <v>200.4</v>
+        <v>214.1</v>
       </c>
       <c r="G10" s="10">
-        <v>185.7</v>
+        <v>197.4</v>
       </c>
       <c r="H10" s="10">
-        <v>77.1</v>
+        <v>75.4</v>
       </c>
       <c r="I10" s="10">
-        <v>135.9</v>
+        <v>139.7</v>
       </c>
       <c r="J10" s="10">
-        <v>76.8</v>
+        <v>75.9</v>
       </c>
       <c r="K10" s="10">
-        <v>129.8</v>
+        <v>133.5</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" ht="14.9324" customHeight="1">
@@ -614,31 +621,31 @@
         <v>13</v>
       </c>
       <c r="C11" s="9">
-        <v>146.7</v>
+        <v>157.8</v>
       </c>
       <c r="D11" s="9">
-        <v>185.2</v>
+        <v>198.3</v>
       </c>
       <c r="E11" s="9">
-        <v>163.5</v>
+        <v>182.7</v>
       </c>
       <c r="F11" s="9">
-        <v>178.1</v>
+        <v>200.4</v>
       </c>
       <c r="G11" s="9">
-        <v>170.6</v>
+        <v>185.7</v>
       </c>
       <c r="H11" s="9">
-        <v>76.6</v>
+        <v>77.1</v>
       </c>
       <c r="I11" s="9">
-        <v>131.2</v>
+        <v>135.9</v>
       </c>
       <c r="J11" s="9">
-        <v>72.4</v>
+        <v>76.8</v>
       </c>
       <c r="K11" s="9">
-        <v>125.1</v>
+        <v>129.8</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="14.9324" customHeight="1">
@@ -646,31 +653,31 @@
         <v>14</v>
       </c>
       <c r="C12" s="10">
-        <v>136.065258</v>
+        <v>146.7</v>
       </c>
       <c r="D12" s="10">
-        <v>170.119099</v>
+        <v>185.2</v>
       </c>
       <c r="E12" s="10">
-        <v>142.339972</v>
+        <v>163.5</v>
       </c>
       <c r="F12" s="10">
-        <v>163.017028</v>
+        <v>178.1</v>
       </c>
       <c r="G12" s="10">
-        <v>156.947712</v>
+        <v>170.6</v>
       </c>
       <c r="H12" s="10">
-        <v>77.946401</v>
+        <v>76.6</v>
       </c>
       <c r="I12" s="10">
-        <v>125.143144</v>
+        <v>131.2</v>
       </c>
       <c r="J12" s="10">
-        <v>71.278846</v>
+        <v>72.4</v>
       </c>
       <c r="K12" s="10">
-        <v>112.42022</v>
+        <v>125.1</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" ht="14.9324" customHeight="1">
@@ -678,31 +685,31 @@
         <v>15</v>
       </c>
       <c r="C13" s="9">
-        <v>123.2</v>
+        <v>136.065258</v>
       </c>
       <c r="D13" s="9">
-        <v>157.6</v>
+        <v>170.119099</v>
       </c>
       <c r="E13" s="9">
-        <v>131.1</v>
+        <v>142.339972</v>
       </c>
       <c r="F13" s="9">
-        <v>139.4</v>
+        <v>163.017028</v>
       </c>
       <c r="G13" s="9">
-        <v>130</v>
+        <v>156.947712</v>
       </c>
       <c r="H13" s="9">
-        <v>80.1</v>
+        <v>77.946401</v>
       </c>
       <c r="I13" s="9">
-        <v>114.9</v>
+        <v>125.143144</v>
       </c>
       <c r="J13" s="9">
-        <v>59.8</v>
+        <v>71.278846</v>
       </c>
       <c r="K13" s="9">
-        <v>111.6</v>
+        <v>112.42022</v>
       </c>
     </row>
     <row r="14" s="1" customFormat="1" ht="14.9324" customHeight="1">
@@ -710,31 +717,31 @@
         <v>16</v>
       </c>
       <c r="C14" s="10">
-        <v>131.6</v>
+        <v>123.2</v>
       </c>
       <c r="D14" s="10">
-        <v>158.4</v>
+        <v>157.6</v>
       </c>
       <c r="E14" s="10">
-        <v>133.6</v>
+        <v>131.1</v>
       </c>
       <c r="F14" s="10">
-        <v>152.6</v>
+        <v>139.4</v>
       </c>
       <c r="G14" s="10">
-        <v>145.7</v>
+        <v>130</v>
       </c>
       <c r="H14" s="10">
-        <v>84.5</v>
+        <v>80.1</v>
       </c>
       <c r="I14" s="10">
-        <v>129.4</v>
+        <v>114.9</v>
       </c>
       <c r="J14" s="10">
-        <v>65.1</v>
+        <v>59.8</v>
       </c>
       <c r="K14" s="10">
-        <v>109.8</v>
+        <v>111.6</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" ht="14.9324" customHeight="1">
@@ -742,31 +749,31 @@
         <v>17</v>
       </c>
       <c r="C15" s="9">
-        <v>131.2</v>
+        <v>131.6</v>
       </c>
       <c r="D15" s="9">
-        <v>156.9</v>
+        <v>158.4</v>
       </c>
       <c r="E15" s="9">
-        <v>134.1</v>
+        <v>133.6</v>
       </c>
       <c r="F15" s="9">
-        <v>147.7</v>
+        <v>152.6</v>
       </c>
       <c r="G15" s="9">
-        <v>147</v>
+        <v>145.7</v>
       </c>
       <c r="H15" s="9">
-        <v>89.8</v>
+        <v>84.5</v>
       </c>
       <c r="I15" s="9">
-        <v>129.1</v>
+        <v>129.4</v>
       </c>
       <c r="J15" s="9">
-        <v>69</v>
+        <v>65.1</v>
       </c>
       <c r="K15" s="9">
-        <v>107</v>
+        <v>109.8</v>
       </c>
     </row>
     <row r="16" s="1" customFormat="1" ht="14.9324" customHeight="1">
@@ -774,31 +781,31 @@
         <v>18</v>
       </c>
       <c r="C16" s="10">
-        <v>125.687808</v>
+        <v>131.2</v>
       </c>
       <c r="D16" s="10">
-        <v>149.175567</v>
+        <v>156.9</v>
       </c>
       <c r="E16" s="10">
-        <v>124.87884</v>
+        <v>134.1</v>
       </c>
       <c r="F16" s="10">
-        <v>140.512834</v>
+        <v>147.7</v>
       </c>
       <c r="G16" s="10">
-        <v>129.721569</v>
+        <v>147</v>
       </c>
       <c r="H16" s="10">
-        <v>93.683831</v>
+        <v>89.8</v>
       </c>
       <c r="I16" s="10">
-        <v>125.195118</v>
+        <v>129.1</v>
       </c>
       <c r="J16" s="10">
-        <v>68.422978</v>
+        <v>69</v>
       </c>
       <c r="K16" s="10">
-        <v>106.614714</v>
+        <v>107</v>
       </c>
     </row>
     <row r="17" s="1" customFormat="1" ht="14.9324" customHeight="1">
@@ -806,31 +813,31 @@
         <v>19</v>
       </c>
       <c r="C17" s="9">
-        <v>120.532393</v>
+        <v>125.687808</v>
       </c>
       <c r="D17" s="9">
-        <v>141.639232</v>
+        <v>149.175567</v>
       </c>
       <c r="E17" s="9">
-        <v>121.754526</v>
+        <v>124.87884</v>
       </c>
       <c r="F17" s="9">
-        <v>133.093782</v>
+        <v>140.512834</v>
       </c>
       <c r="G17" s="9">
-        <v>121.993464</v>
+        <v>129.721569</v>
       </c>
       <c r="H17" s="9">
-        <v>94.536989</v>
+        <v>93.683831</v>
       </c>
       <c r="I17" s="9">
-        <v>119.713745</v>
+        <v>125.195118</v>
       </c>
       <c r="J17" s="9">
-        <v>66.520709</v>
+        <v>68.422978</v>
       </c>
       <c r="K17" s="9">
-        <v>106.57758</v>
+        <v>106.614714</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="14.9324" customHeight="1">
@@ -838,31 +845,31 @@
         <v>20</v>
       </c>
       <c r="C18" s="10">
-        <v>115.060302</v>
+        <v>120.532393</v>
       </c>
       <c r="D18" s="10">
-        <v>133.827638</v>
+        <v>141.639232</v>
       </c>
       <c r="E18" s="10">
-        <v>117.99418</v>
+        <v>121.754526</v>
       </c>
       <c r="F18" s="10">
-        <v>120.189704</v>
+        <v>133.093782</v>
       </c>
       <c r="G18" s="10">
-        <v>123.510675</v>
+        <v>121.993464</v>
       </c>
       <c r="H18" s="10">
-        <v>96.98628</v>
+        <v>94.536989</v>
       </c>
       <c r="I18" s="10">
-        <v>114.13473</v>
+        <v>119.713745</v>
       </c>
       <c r="J18" s="10">
-        <v>67.215515</v>
+        <v>66.520709</v>
       </c>
       <c r="K18" s="10">
-        <v>106.356324</v>
+        <v>106.57758</v>
       </c>
     </row>
     <row r="19" s="1" customFormat="1" ht="14.9324" customHeight="1">
@@ -870,31 +877,31 @@
         <v>21</v>
       </c>
       <c r="C19" s="9">
-        <v>111.733871</v>
+        <v>115.060302</v>
       </c>
       <c r="D19" s="9">
-        <v>126.627234</v>
+        <v>133.827638</v>
       </c>
       <c r="E19" s="9">
-        <v>112.553282</v>
+        <v>117.99418</v>
       </c>
       <c r="F19" s="9">
-        <v>121.744587</v>
+        <v>120.189704</v>
       </c>
       <c r="G19" s="9">
-        <v>118.055773</v>
+        <v>123.510675</v>
       </c>
       <c r="H19" s="9">
-        <v>98.350059</v>
+        <v>96.98628</v>
       </c>
       <c r="I19" s="9">
-        <v>108.825517</v>
+        <v>114.13473</v>
       </c>
       <c r="J19" s="9">
-        <v>70.546131</v>
+        <v>67.215515</v>
       </c>
       <c r="K19" s="9">
-        <v>99.382909</v>
+        <v>106.356324</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" ht="14.9324" customHeight="1">
@@ -902,394 +909,394 @@
         <v>22</v>
       </c>
       <c r="C20" s="10">
+        <v>111.733871</v>
+      </c>
+      <c r="D20" s="10">
+        <v>126.627234</v>
+      </c>
+      <c r="E20" s="10">
+        <v>112.553282</v>
+      </c>
+      <c r="F20" s="10">
+        <v>121.744587</v>
+      </c>
+      <c r="G20" s="10">
+        <v>118.055773</v>
+      </c>
+      <c r="H20" s="10">
+        <v>98.350059</v>
+      </c>
+      <c r="I20" s="10">
+        <v>108.825517</v>
+      </c>
+      <c r="J20" s="10">
+        <v>70.546131</v>
+      </c>
+      <c r="K20" s="10">
+        <v>99.382909</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" ht="14.9324" customHeight="1">
+      <c r="B21" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C21" s="9">
         <v>106.474908</v>
       </c>
-      <c r="D20" s="10">
+      <c r="D21" s="9">
         <v>110.295613</v>
       </c>
-      <c r="E20" s="10">
+      <c r="E21" s="9">
         <v>104.169197</v>
       </c>
-      <c r="F20" s="10">
+      <c r="F21" s="9">
         <v>115.82097</v>
       </c>
-      <c r="G20" s="10">
+      <c r="G21" s="9">
         <v>111.471024</v>
       </c>
-      <c r="H20" s="10">
+      <c r="H21" s="9">
         <v>99.209156</v>
       </c>
-      <c r="I20" s="10">
+      <c r="I21" s="9">
         <v>108.638904</v>
       </c>
-      <c r="J20" s="10">
+      <c r="J21" s="9">
         <v>74.521141</v>
       </c>
-      <c r="K20" s="10">
+      <c r="K21" s="9">
         <v>98.109787</v>
       </c>
     </row>
-    <row r="21" s="1" customFormat="1" ht="14.9324" customHeight="1">
-      <c r="B21" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="C21" s="12">
+    <row r="22" s="1" customFormat="1" ht="14.9324" customHeight="1">
+      <c r="B22" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C22" s="12">
         <v>103.816045</v>
       </c>
-      <c r="D21" s="12">
+      <c r="D22" s="12">
         <v>104.003229</v>
       </c>
-      <c r="E21" s="12">
+      <c r="E22" s="12">
         <v>103.188498</v>
       </c>
-      <c r="F21" s="12">
+      <c r="F22" s="12">
         <v>107.917091</v>
       </c>
-      <c r="G21" s="12">
+      <c r="G22" s="12">
         <v>107.457081</v>
       </c>
-      <c r="H21" s="12">
+      <c r="H22" s="12">
         <v>99.402242</v>
       </c>
-      <c r="I21" s="12">
+      <c r="I22" s="12">
         <v>107.152632</v>
       </c>
-      <c r="J21" s="12">
+      <c r="J22" s="12">
         <v>85.576418</v>
       </c>
-      <c r="K21" s="12">
+      <c r="K22" s="12">
         <v>96.684778</v>
       </c>
     </row>
-    <row r="22" s="1" customFormat="1" ht="19.7321" customHeight="1"/>
-    <row r="23" s="1" customFormat="1" ht="14.3991" customHeight="1">
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-    </row>
-    <row r="24" s="1" customFormat="1" ht="12.7992" customHeight="1">
-      <c r="B24" s="15" t="s">
-        <v>48</v>
-      </c>
-      <c r="C24" s="15"/>
+    <row r="23" s="1" customFormat="1" ht="19.7321" customHeight="1"/>
+    <row r="24" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="D24" s="15"/>
-    </row>
-    <row r="25" s="1" customFormat="1" ht="27.1983" customHeight="1">
-      <c r="B25" s="2" t="s">
+      <c r="E24" s="15"/>
+    </row>
+    <row r="25" s="1" customFormat="1" ht="12.7992" customHeight="1">
+      <c r="B25" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="C25" s="16"/>
+      <c r="D25" s="16"/>
+    </row>
+    <row r="26" s="1" customFormat="1" ht="27.1983" customHeight="1">
+      <c r="B26" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C25" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D25" s="3" t="s">
+      <c r="C26" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E25" s="3" t="s">
+      <c r="E26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F25" s="3" t="s">
+      <c r="F26" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G25" s="3" t="s">
+      <c r="G26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H25" s="3" t="s">
+      <c r="H26" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="I25" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="J25" s="3" t="s">
+      <c r="I26" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="J26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K25" s="3" t="s">
+      <c r="K26" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="26" s="1" customFormat="1" ht="18.1322" customHeight="1">
-      <c r="B26" s="4">
+    <row r="27" s="1" customFormat="1" ht="18.1322" customHeight="1">
+      <c r="B27" s="4">
         <v>1</v>
       </c>
-      <c r="C26" s="5">
+      <c r="C27" s="5">
         <v>2</v>
       </c>
-      <c r="D26" s="5">
+      <c r="D27" s="5">
         <v>3</v>
       </c>
-      <c r="E26" s="5">
+      <c r="E27" s="5">
         <v>4</v>
       </c>
-      <c r="F26" s="5">
+      <c r="F27" s="5">
         <v>5</v>
       </c>
-      <c r="G26" s="5">
+      <c r="G27" s="5">
         <v>6</v>
       </c>
-      <c r="H26" s="5">
+      <c r="H27" s="5">
         <v>7</v>
       </c>
-      <c r="I26" s="5">
+      <c r="I27" s="5">
         <v>8</v>
       </c>
-      <c r="J26" s="5">
+      <c r="J27" s="5">
         <v>9</v>
       </c>
-      <c r="K26" s="5">
+      <c r="K27" s="5">
         <v>10</v>
       </c>
     </row>
-    <row r="27" s="1" customFormat="1" ht="14.9324" customHeight="1">
-      <c r="B27" s="6" t="s">
+    <row r="28" s="1" customFormat="1" ht="14.9324" customHeight="1">
+      <c r="B28" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C27" s="7">
+      <c r="C28" s="7">
         <v>37.9</v>
       </c>
-      <c r="D27" s="7">
+      <c r="D28" s="7">
         <v>10.32</v>
       </c>
-      <c r="E27" s="7">
+      <c r="E28" s="7">
         <v>4.38</v>
       </c>
-      <c r="F27" s="7">
+      <c r="F28" s="7">
         <v>6.68</v>
       </c>
-      <c r="G27" s="7">
+      <c r="G28" s="7">
         <v>2.41</v>
       </c>
-      <c r="H27" s="7">
+      <c r="H28" s="7">
         <v>5.22</v>
       </c>
-      <c r="I27" s="7">
+      <c r="I28" s="7">
         <v>5.94</v>
       </c>
-      <c r="J27" s="7">
+      <c r="J28" s="7">
         <v>1.71</v>
       </c>
-      <c r="K27" s="7">
+      <c r="K28" s="7">
         <v>1.25</v>
-      </c>
-    </row>
-    <row r="28" s="1" customFormat="1" ht="14.9324" customHeight="1">
-      <c r="B28" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C28" s="9">
-        <v>175.2</v>
-      </c>
-      <c r="D28" s="9">
-        <v>193.4</v>
-      </c>
-      <c r="E28" s="9">
-        <v>169.5</v>
-      </c>
-      <c r="F28" s="9">
-        <v>211.3</v>
-      </c>
-      <c r="G28" s="9">
-        <v>215.5</v>
-      </c>
-      <c r="H28" s="9">
-        <v>108.727</v>
-      </c>
-      <c r="I28" s="9">
-        <v>183.2</v>
-      </c>
-      <c r="J28" s="9">
-        <v>101.6</v>
-      </c>
-      <c r="K28" s="9">
-        <v>114.4</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" ht="14.9324" customHeight="1">
       <c r="B29" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="C29" s="10">
-        <v>168.5</v>
-      </c>
-      <c r="D29" s="10">
-        <v>178.5</v>
-      </c>
-      <c r="E29" s="10">
-        <v>162.2</v>
-      </c>
-      <c r="F29" s="10">
-        <v>211.4</v>
-      </c>
-      <c r="G29" s="10">
-        <v>205.3</v>
-      </c>
-      <c r="H29" s="10">
-        <v>110.2</v>
-      </c>
-      <c r="I29" s="10">
-        <v>175.6</v>
-      </c>
-      <c r="J29" s="10">
-        <v>106</v>
-      </c>
-      <c r="K29" s="10">
-        <v>101.7</v>
+      <c r="C29" s="9">
+        <v>175.2</v>
+      </c>
+      <c r="D29" s="9">
+        <v>193.4</v>
+      </c>
+      <c r="E29" s="9">
+        <v>169.5</v>
+      </c>
+      <c r="F29" s="9">
+        <v>211.3</v>
+      </c>
+      <c r="G29" s="9">
+        <v>215.5</v>
+      </c>
+      <c r="H29" s="9">
+        <v>108.727</v>
+      </c>
+      <c r="I29" s="9">
+        <v>183.2</v>
+      </c>
+      <c r="J29" s="9">
+        <v>101.6</v>
+      </c>
+      <c r="K29" s="9">
+        <v>114.4</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" ht="14.9324" customHeight="1">
       <c r="B30" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="C30" s="9">
-        <v>161.2</v>
-      </c>
-      <c r="D30" s="9">
-        <v>164.6</v>
-      </c>
-      <c r="E30" s="9">
-        <v>150</v>
-      </c>
-      <c r="F30" s="9">
-        <v>201.9</v>
-      </c>
-      <c r="G30" s="9">
-        <v>194.5</v>
-      </c>
-      <c r="H30" s="9">
-        <v>111.2</v>
-      </c>
-      <c r="I30" s="9">
-        <v>175</v>
-      </c>
-      <c r="J30" s="9">
-        <v>111.5</v>
-      </c>
-      <c r="K30" s="9">
-        <v>101.8</v>
+      <c r="C30" s="10">
+        <v>168.5</v>
+      </c>
+      <c r="D30" s="10">
+        <v>178.5</v>
+      </c>
+      <c r="E30" s="10">
+        <v>162.2</v>
+      </c>
+      <c r="F30" s="10">
+        <v>211.4</v>
+      </c>
+      <c r="G30" s="10">
+        <v>205.3</v>
+      </c>
+      <c r="H30" s="10">
+        <v>110.2</v>
+      </c>
+      <c r="I30" s="10">
+        <v>175.6</v>
+      </c>
+      <c r="J30" s="10">
+        <v>106</v>
+      </c>
+      <c r="K30" s="10">
+        <v>101.7</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" ht="14.9324" customHeight="1">
       <c r="B31" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C31" s="10">
-        <v>154.7</v>
-      </c>
-      <c r="D31" s="10">
-        <v>155.3</v>
-      </c>
-      <c r="E31" s="10">
-        <v>148.1</v>
-      </c>
-      <c r="F31" s="10">
-        <v>181.1</v>
-      </c>
-      <c r="G31" s="10">
-        <v>188.7</v>
-      </c>
-      <c r="H31" s="10">
-        <v>111.4</v>
-      </c>
-      <c r="I31" s="10">
-        <v>172.4</v>
-      </c>
-      <c r="J31" s="10">
-        <v>128.1</v>
-      </c>
-      <c r="K31" s="10">
-        <v>100.2</v>
+      <c r="C31" s="9">
+        <v>161.2</v>
+      </c>
+      <c r="D31" s="9">
+        <v>164.6</v>
+      </c>
+      <c r="E31" s="9">
+        <v>150</v>
+      </c>
+      <c r="F31" s="9">
+        <v>201.9</v>
+      </c>
+      <c r="G31" s="9">
+        <v>194.5</v>
+      </c>
+      <c r="H31" s="9">
+        <v>111.2</v>
+      </c>
+      <c r="I31" s="9">
+        <v>175</v>
+      </c>
+      <c r="J31" s="9">
+        <v>111.5</v>
+      </c>
+      <c r="K31" s="9">
+        <v>101.8</v>
       </c>
     </row>
     <row r="32" s="1" customFormat="1" ht="14.9324" customHeight="1">
       <c r="B32" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C32" s="9">
-        <v>145.3</v>
-      </c>
-      <c r="D32" s="9">
-        <v>149.3</v>
-      </c>
-      <c r="E32" s="9">
-        <v>141.5</v>
-      </c>
-      <c r="F32" s="9">
-        <v>174</v>
-      </c>
-      <c r="G32" s="9">
-        <v>175.2</v>
-      </c>
-      <c r="H32" s="9">
-        <v>112.1</v>
-      </c>
-      <c r="I32" s="9">
-        <v>133.7</v>
-      </c>
-      <c r="J32" s="9">
-        <v>149.8</v>
-      </c>
-      <c r="K32" s="9">
-        <v>103.8</v>
+        <v>24</v>
+      </c>
+      <c r="C32" s="10">
+        <v>154.7</v>
+      </c>
+      <c r="D32" s="10">
+        <v>155.3</v>
+      </c>
+      <c r="E32" s="10">
+        <v>148.1</v>
+      </c>
+      <c r="F32" s="10">
+        <v>181.1</v>
+      </c>
+      <c r="G32" s="10">
+        <v>188.7</v>
+      </c>
+      <c r="H32" s="10">
+        <v>111.4</v>
+      </c>
+      <c r="I32" s="10">
+        <v>172.4</v>
+      </c>
+      <c r="J32" s="10">
+        <v>128.1</v>
+      </c>
+      <c r="K32" s="10">
+        <v>100.2</v>
       </c>
     </row>
     <row r="33" s="1" customFormat="1" ht="14.9324" customHeight="1">
       <c r="B33" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="C33" s="10">
-        <v>138.4</v>
-      </c>
-      <c r="D33" s="10">
-        <v>138.1</v>
-      </c>
-      <c r="E33" s="10">
-        <v>139.7</v>
-      </c>
-      <c r="F33" s="10">
-        <v>157.7</v>
-      </c>
-      <c r="G33" s="10">
-        <v>164.2</v>
-      </c>
-      <c r="H33" s="10">
-        <v>111</v>
-      </c>
-      <c r="I33" s="10">
-        <v>129.7</v>
-      </c>
-      <c r="J33" s="10">
-        <v>164.4</v>
-      </c>
-      <c r="K33" s="10">
-        <v>103.4</v>
+      <c r="C33" s="9">
+        <v>145.3</v>
+      </c>
+      <c r="D33" s="9">
+        <v>149.3</v>
+      </c>
+      <c r="E33" s="9">
+        <v>141.5</v>
+      </c>
+      <c r="F33" s="9">
+        <v>174</v>
+      </c>
+      <c r="G33" s="9">
+        <v>175.2</v>
+      </c>
+      <c r="H33" s="9">
+        <v>112.1</v>
+      </c>
+      <c r="I33" s="9">
+        <v>133.7</v>
+      </c>
+      <c r="J33" s="9">
+        <v>149.8</v>
+      </c>
+      <c r="K33" s="9">
+        <v>103.8</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" ht="14.9324" customHeight="1">
       <c r="B34" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="C34" s="9">
-        <v>129.9</v>
-      </c>
-      <c r="D34" s="9">
-        <v>130.8</v>
-      </c>
-      <c r="E34" s="9">
-        <v>140</v>
-      </c>
-      <c r="F34" s="9">
-        <v>139.3</v>
-      </c>
-      <c r="G34" s="9">
-        <v>157.1</v>
-      </c>
-      <c r="H34" s="9">
-        <v>99.1</v>
-      </c>
-      <c r="I34" s="9">
-        <v>125.9</v>
-      </c>
-      <c r="J34" s="9">
-        <v>149.5</v>
-      </c>
-      <c r="K34" s="9">
+      <c r="C34" s="10">
+        <v>138.4</v>
+      </c>
+      <c r="D34" s="10">
+        <v>138.1</v>
+      </c>
+      <c r="E34" s="10">
+        <v>139.7</v>
+      </c>
+      <c r="F34" s="10">
+        <v>157.7</v>
+      </c>
+      <c r="G34" s="10">
+        <v>164.2</v>
+      </c>
+      <c r="H34" s="10">
+        <v>111</v>
+      </c>
+      <c r="I34" s="10">
+        <v>129.7</v>
+      </c>
+      <c r="J34" s="10">
+        <v>164.4</v>
+      </c>
+      <c r="K34" s="10">
         <v>103.4</v>
       </c>
     </row>
@@ -1297,532 +1304,565 @@
       <c r="B35" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="C35" s="10">
-        <v>121.8</v>
-      </c>
-      <c r="D35" s="10">
-        <v>123.2</v>
-      </c>
-      <c r="E35" s="10">
-        <v>129.5</v>
-      </c>
-      <c r="F35" s="10">
-        <v>131.4</v>
-      </c>
-      <c r="G35" s="10">
-        <v>142.1</v>
-      </c>
-      <c r="H35" s="10">
-        <v>98.6</v>
-      </c>
-      <c r="I35" s="10">
-        <v>126.5</v>
-      </c>
-      <c r="J35" s="10">
+      <c r="C35" s="9">
+        <v>129.9</v>
+      </c>
+      <c r="D35" s="9">
+        <v>130.8</v>
+      </c>
+      <c r="E35" s="9">
+        <v>140</v>
+      </c>
+      <c r="F35" s="9">
+        <v>139.3</v>
+      </c>
+      <c r="G35" s="9">
+        <v>157.1</v>
+      </c>
+      <c r="H35" s="9">
+        <v>99.1</v>
+      </c>
+      <c r="I35" s="9">
+        <v>125.9</v>
+      </c>
+      <c r="J35" s="9">
+        <v>149.5</v>
+      </c>
+      <c r="K35" s="9">
         <v>103.4</v>
-      </c>
-      <c r="K35" s="10">
-        <v>91.8</v>
       </c>
     </row>
     <row r="36" s="1" customFormat="1" ht="14.9324" customHeight="1">
       <c r="B36" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="C36" s="9">
-        <v>118.5</v>
-      </c>
-      <c r="D36" s="9">
-        <v>119.9</v>
-      </c>
-      <c r="E36" s="9">
-        <v>119.9</v>
-      </c>
-      <c r="F36" s="9">
-        <v>128.9</v>
-      </c>
-      <c r="G36" s="9">
-        <v>132.5</v>
-      </c>
-      <c r="H36" s="9">
-        <v>100.4</v>
-      </c>
-      <c r="I36" s="9">
-        <v>122.8</v>
-      </c>
-      <c r="J36" s="9">
-        <v>102.1</v>
-      </c>
-      <c r="K36" s="9">
-        <v>95.5</v>
+      <c r="C36" s="10">
+        <v>121.8</v>
+      </c>
+      <c r="D36" s="10">
+        <v>123.2</v>
+      </c>
+      <c r="E36" s="10">
+        <v>129.5</v>
+      </c>
+      <c r="F36" s="10">
+        <v>131.4</v>
+      </c>
+      <c r="G36" s="10">
+        <v>142.1</v>
+      </c>
+      <c r="H36" s="10">
+        <v>98.6</v>
+      </c>
+      <c r="I36" s="10">
+        <v>126.5</v>
+      </c>
+      <c r="J36" s="10">
+        <v>103.4</v>
+      </c>
+      <c r="K36" s="10">
+        <v>91.8</v>
       </c>
     </row>
     <row r="37" s="1" customFormat="1" ht="14.9324" customHeight="1">
       <c r="B37" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C37" s="10">
+      <c r="C37" s="9">
+        <v>118.5</v>
+      </c>
+      <c r="D37" s="9">
+        <v>119.9</v>
+      </c>
+      <c r="E37" s="9">
+        <v>119.9</v>
+      </c>
+      <c r="F37" s="9">
+        <v>128.9</v>
+      </c>
+      <c r="G37" s="9">
+        <v>132.5</v>
+      </c>
+      <c r="H37" s="9">
+        <v>100.4</v>
+      </c>
+      <c r="I37" s="9">
+        <v>122.8</v>
+      </c>
+      <c r="J37" s="9">
+        <v>102.1</v>
+      </c>
+      <c r="K37" s="9">
+        <v>95.5</v>
+      </c>
+    </row>
+    <row r="38" s="1" customFormat="1" ht="14.9324" customHeight="1">
+      <c r="B38" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C38" s="10">
         <v>112.6</v>
       </c>
-      <c r="D37" s="10">
+      <c r="D38" s="10">
         <v>112.8</v>
       </c>
-      <c r="E37" s="10">
+      <c r="E38" s="10">
         <v>112.9</v>
       </c>
-      <c r="F37" s="10">
+      <c r="F38" s="10">
         <v>120.7</v>
       </c>
-      <c r="G37" s="10">
+      <c r="G38" s="10">
         <v>122.6</v>
       </c>
-      <c r="H37" s="10">
+      <c r="H38" s="10">
         <v>100</v>
       </c>
-      <c r="I37" s="10">
+      <c r="I38" s="10">
         <v>115.3</v>
       </c>
-      <c r="J37" s="10">
+      <c r="J38" s="10">
         <v>99.9</v>
       </c>
-      <c r="K37" s="10">
+      <c r="K38" s="10">
         <v>103.8</v>
       </c>
     </row>
-    <row r="38" s="1" customFormat="1" ht="14.9324" customHeight="1">
-      <c r="B38" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="C38" s="12">
+    <row r="39" s="1" customFormat="1" ht="14.9324" customHeight="1">
+      <c r="B39" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C39" s="13">
         <v>103.8687</v>
       </c>
-      <c r="D38" s="12">
+      <c r="D39" s="13">
         <v>105.1203</v>
       </c>
-      <c r="E38" s="12">
+      <c r="E39" s="13">
         <v>106.5544</v>
       </c>
-      <c r="F38" s="12">
+      <c r="F39" s="13">
         <v>107.0163</v>
       </c>
-      <c r="G38" s="12">
+      <c r="G39" s="13">
         <v>112.3</v>
       </c>
-      <c r="H38" s="12">
+      <c r="H39" s="13">
         <v>94.7</v>
       </c>
-      <c r="I38" s="12">
+      <c r="I39" s="13">
         <v>102.2</v>
       </c>
-      <c r="J38" s="12">
+      <c r="J39" s="13">
         <v>101.3853</v>
       </c>
-      <c r="K38" s="12">
+      <c r="K39" s="13">
         <v>100.6224</v>
       </c>
     </row>
-    <row r="39" s="1" customFormat="1" ht="19.7321" customHeight="1"/>
-    <row r="40" s="1" customFormat="1" ht="14.3991" customHeight="1">
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-    </row>
-    <row r="41" s="1" customFormat="1" ht="12.7992" customHeight="1">
-      <c r="B41" s="15" t="s">
-        <v>49</v>
-      </c>
-      <c r="C41" s="15"/>
+    <row r="40" s="1" customFormat="1" ht="19.7321" customHeight="1"/>
+    <row r="41" s="1" customFormat="1" ht="14.3991" customHeight="1">
       <c r="D41" s="15"/>
-    </row>
-    <row r="42" s="1" customFormat="1" ht="39.9975" customHeight="1">
-      <c r="B42" s="2" t="s">
+      <c r="E41" s="15"/>
+    </row>
+    <row r="42" s="1" customFormat="1" ht="12.7992" customHeight="1">
+      <c r="B42" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="C42" s="16"/>
+      <c r="D42" s="16"/>
+    </row>
+    <row r="43" s="1" customFormat="1" ht="39.9975" customHeight="1">
+      <c r="B43" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C42" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D42" s="3" t="s">
+      <c r="C43" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D43" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E42" s="3" t="s">
+      <c r="E43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F42" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="G42" s="3" t="s">
+      <c r="F43" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G43" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H42" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I42" s="3" t="s">
+      <c r="H43" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I43" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="43" s="1" customFormat="1" ht="18.1322" customHeight="1">
-      <c r="B43" s="4">
+    <row r="44" s="1" customFormat="1" ht="18.1322" customHeight="1">
+      <c r="B44" s="4">
         <v>1</v>
       </c>
-      <c r="C43" s="5">
+      <c r="C44" s="5">
         <v>2</v>
       </c>
-      <c r="D43" s="5">
+      <c r="D44" s="5">
         <v>3</v>
       </c>
-      <c r="E43" s="5">
+      <c r="E44" s="5">
         <v>4</v>
       </c>
-      <c r="F43" s="5">
+      <c r="F44" s="5">
         <v>5</v>
       </c>
-      <c r="G43" s="5">
+      <c r="G44" s="5">
         <v>6</v>
       </c>
-      <c r="H43" s="5">
+      <c r="H44" s="5">
         <v>7</v>
       </c>
-      <c r="I43" s="5">
+      <c r="I44" s="5">
         <v>8</v>
       </c>
     </row>
-    <row r="44" s="1" customFormat="1" ht="14.9324" customHeight="1">
-      <c r="B44" s="6" t="s">
+    <row r="45" s="1" customFormat="1" ht="14.9324" customHeight="1">
+      <c r="B45" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C44" s="7">
+      <c r="C45" s="7">
         <v>26.68</v>
       </c>
-      <c r="D44" s="7">
+      <c r="D45" s="7">
         <v>10.17</v>
       </c>
-      <c r="E44" s="7">
+      <c r="E45" s="7">
         <v>3.22</v>
       </c>
-      <c r="F44" s="7">
+      <c r="F45" s="7">
         <v>5.13</v>
       </c>
-      <c r="G44" s="7">
+      <c r="G45" s="7">
         <v>1.99</v>
       </c>
-      <c r="H44" s="7">
+      <c r="H45" s="7">
         <v>4.17</v>
       </c>
-      <c r="I44" s="7">
+      <c r="I45" s="7">
         <v>2</v>
-      </c>
-    </row>
-    <row r="45" s="1" customFormat="1" ht="14.9324" customHeight="1">
-      <c r="B45" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C45" s="9">
-        <v>193</v>
-      </c>
-      <c r="D45" s="9">
-        <v>181.6</v>
-      </c>
-      <c r="E45" s="9">
-        <v>153.1</v>
-      </c>
-      <c r="F45" s="9">
-        <v>263.5</v>
-      </c>
-      <c r="G45" s="9">
-        <v>229.5</v>
-      </c>
-      <c r="H45" s="9">
-        <v>125.8</v>
-      </c>
-      <c r="I45" s="9">
-        <v>238.1</v>
       </c>
     </row>
     <row r="46" s="1" customFormat="1" ht="14.9324" customHeight="1">
       <c r="B46" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="C46" s="10">
-        <v>182.4</v>
-      </c>
-      <c r="D46" s="10">
-        <v>172.6</v>
-      </c>
-      <c r="E46" s="10">
-        <v>144.2</v>
-      </c>
-      <c r="F46" s="10">
-        <v>243.1</v>
-      </c>
-      <c r="G46" s="10">
-        <v>215.3</v>
-      </c>
-      <c r="H46" s="10">
-        <v>123.5</v>
-      </c>
-      <c r="I46" s="10">
-        <v>228.3</v>
+      <c r="C46" s="9">
+        <v>193</v>
+      </c>
+      <c r="D46" s="9">
+        <v>181.6</v>
+      </c>
+      <c r="E46" s="9">
+        <v>153.1</v>
+      </c>
+      <c r="F46" s="9">
+        <v>263.5</v>
+      </c>
+      <c r="G46" s="9">
+        <v>229.5</v>
+      </c>
+      <c r="H46" s="9">
+        <v>125.8</v>
+      </c>
+      <c r="I46" s="9">
+        <v>238.1</v>
       </c>
     </row>
     <row r="47" s="1" customFormat="1" ht="14.9324" customHeight="1">
       <c r="B47" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="C47" s="9">
-        <v>171.9</v>
-      </c>
-      <c r="D47" s="9">
-        <v>164.3</v>
-      </c>
-      <c r="E47" s="9">
-        <v>137.2</v>
-      </c>
-      <c r="F47" s="9">
-        <v>221.5</v>
-      </c>
-      <c r="G47" s="9">
-        <v>203</v>
-      </c>
-      <c r="H47" s="9">
-        <v>122.6</v>
-      </c>
-      <c r="I47" s="9">
-        <v>210.9</v>
+      <c r="C47" s="10">
+        <v>182.4</v>
+      </c>
+      <c r="D47" s="10">
+        <v>172.6</v>
+      </c>
+      <c r="E47" s="10">
+        <v>144.2</v>
+      </c>
+      <c r="F47" s="10">
+        <v>243.1</v>
+      </c>
+      <c r="G47" s="10">
+        <v>215.3</v>
+      </c>
+      <c r="H47" s="10">
+        <v>123.5</v>
+      </c>
+      <c r="I47" s="10">
+        <v>228.3</v>
       </c>
     </row>
     <row r="48" s="1" customFormat="1" ht="14.9324" customHeight="1">
       <c r="B48" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C48" s="10">
-        <v>163.7</v>
-      </c>
-      <c r="D48" s="10">
-        <v>159.3</v>
-      </c>
-      <c r="E48" s="10">
-        <v>131.2</v>
-      </c>
-      <c r="F48" s="10">
-        <v>206.4</v>
-      </c>
-      <c r="G48" s="10">
-        <v>186.5</v>
-      </c>
-      <c r="H48" s="10">
-        <v>118.5</v>
-      </c>
-      <c r="I48" s="10">
-        <v>201</v>
+      <c r="C48" s="9">
+        <v>171.9</v>
+      </c>
+      <c r="D48" s="9">
+        <v>164.3</v>
+      </c>
+      <c r="E48" s="9">
+        <v>137.2</v>
+      </c>
+      <c r="F48" s="9">
+        <v>221.5</v>
+      </c>
+      <c r="G48" s="9">
+        <v>203</v>
+      </c>
+      <c r="H48" s="9">
+        <v>122.6</v>
+      </c>
+      <c r="I48" s="9">
+        <v>210.9</v>
       </c>
     </row>
     <row r="49" s="1" customFormat="1" ht="14.9324" customHeight="1">
       <c r="B49" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="C49" s="9">
-        <v>158.6</v>
-      </c>
-      <c r="D49" s="9">
-        <v>154.4</v>
-      </c>
-      <c r="E49" s="9">
-        <v>125.9</v>
-      </c>
-      <c r="F49" s="9">
-        <v>199.3</v>
-      </c>
-      <c r="G49" s="9">
-        <v>173.6</v>
-      </c>
-      <c r="H49" s="9">
-        <v>120</v>
-      </c>
-      <c r="I49" s="9">
-        <v>193.8</v>
+      <c r="C49" s="10">
+        <v>163.7</v>
+      </c>
+      <c r="D49" s="10">
+        <v>159.3</v>
+      </c>
+      <c r="E49" s="10">
+        <v>131.2</v>
+      </c>
+      <c r="F49" s="10">
+        <v>206.4</v>
+      </c>
+      <c r="G49" s="10">
+        <v>186.5</v>
+      </c>
+      <c r="H49" s="10">
+        <v>118.5</v>
+      </c>
+      <c r="I49" s="10">
+        <v>201</v>
       </c>
     </row>
     <row r="50" s="1" customFormat="1" ht="14.9324" customHeight="1">
       <c r="B50" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="C50" s="10">
-        <v>150.9</v>
-      </c>
-      <c r="D50" s="10">
-        <v>148.6</v>
-      </c>
-      <c r="E50" s="10">
-        <v>121.6</v>
-      </c>
-      <c r="F50" s="10">
-        <v>187.3</v>
-      </c>
-      <c r="G50" s="10">
-        <v>175.2</v>
-      </c>
-      <c r="H50" s="10">
-        <v>118.2</v>
-      </c>
-      <c r="I50" s="10">
-        <v>161</v>
+      <c r="C50" s="9">
+        <v>158.6</v>
+      </c>
+      <c r="D50" s="9">
+        <v>154.4</v>
+      </c>
+      <c r="E50" s="9">
+        <v>125.9</v>
+      </c>
+      <c r="F50" s="9">
+        <v>199.3</v>
+      </c>
+      <c r="G50" s="9">
+        <v>173.6</v>
+      </c>
+      <c r="H50" s="9">
+        <v>120</v>
+      </c>
+      <c r="I50" s="9">
+        <v>193.8</v>
       </c>
     </row>
     <row r="51" s="1" customFormat="1" ht="14.9324" customHeight="1">
       <c r="B51" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="C51" s="9">
-        <v>138.3</v>
-      </c>
-      <c r="D51" s="9">
-        <v>138.6</v>
-      </c>
-      <c r="E51" s="9">
-        <v>117.8</v>
-      </c>
-      <c r="F51" s="9">
-        <v>162.8</v>
-      </c>
-      <c r="G51" s="9">
-        <v>153.4</v>
-      </c>
-      <c r="H51" s="9">
-        <v>121.1</v>
-      </c>
-      <c r="I51" s="9">
-        <v>128.4</v>
+      <c r="C51" s="10">
+        <v>150.9</v>
+      </c>
+      <c r="D51" s="10">
+        <v>148.6</v>
+      </c>
+      <c r="E51" s="10">
+        <v>121.6</v>
+      </c>
+      <c r="F51" s="10">
+        <v>187.3</v>
+      </c>
+      <c r="G51" s="10">
+        <v>175.2</v>
+      </c>
+      <c r="H51" s="10">
+        <v>118.2</v>
+      </c>
+      <c r="I51" s="10">
+        <v>161</v>
       </c>
     </row>
     <row r="52" s="1" customFormat="1" ht="14.9324" customHeight="1">
       <c r="B52" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="C52" s="10">
-        <v>134.5</v>
-      </c>
-      <c r="D52" s="10">
-        <v>130</v>
-      </c>
-      <c r="E52" s="10">
-        <v>120.3</v>
-      </c>
-      <c r="F52" s="10">
-        <v>160.6</v>
-      </c>
-      <c r="G52" s="10">
-        <v>145.1</v>
-      </c>
-      <c r="H52" s="10">
-        <v>125.3</v>
-      </c>
-      <c r="I52" s="10">
-        <v>122.1</v>
+      <c r="C52" s="9">
+        <v>138.3</v>
+      </c>
+      <c r="D52" s="9">
+        <v>138.6</v>
+      </c>
+      <c r="E52" s="9">
+        <v>117.8</v>
+      </c>
+      <c r="F52" s="9">
+        <v>162.8</v>
+      </c>
+      <c r="G52" s="9">
+        <v>153.4</v>
+      </c>
+      <c r="H52" s="9">
+        <v>121.1</v>
+      </c>
+      <c r="I52" s="9">
+        <v>128.4</v>
       </c>
     </row>
     <row r="53" s="1" customFormat="1" ht="14.9324" customHeight="1">
       <c r="B53" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="C53" s="9">
-        <v>127.3</v>
-      </c>
-      <c r="D53" s="9">
-        <v>121.9</v>
-      </c>
-      <c r="E53" s="9">
-        <v>116.1</v>
-      </c>
-      <c r="F53" s="9">
-        <v>151.1</v>
-      </c>
-      <c r="G53" s="9">
-        <v>133</v>
-      </c>
-      <c r="H53" s="9">
-        <v>121.8</v>
-      </c>
-      <c r="I53" s="9">
-        <v>117.8</v>
+      <c r="C53" s="10">
+        <v>134.5</v>
+      </c>
+      <c r="D53" s="10">
+        <v>130</v>
+      </c>
+      <c r="E53" s="10">
+        <v>120.3</v>
+      </c>
+      <c r="F53" s="10">
+        <v>160.6</v>
+      </c>
+      <c r="G53" s="10">
+        <v>145.1</v>
+      </c>
+      <c r="H53" s="10">
+        <v>125.3</v>
+      </c>
+      <c r="I53" s="10">
+        <v>122.1</v>
       </c>
     </row>
     <row r="54" s="1" customFormat="1" ht="14.9324" customHeight="1">
       <c r="B54" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C54" s="10">
+      <c r="C54" s="9">
+        <v>127.3</v>
+      </c>
+      <c r="D54" s="9">
+        <v>121.9</v>
+      </c>
+      <c r="E54" s="9">
+        <v>116.1</v>
+      </c>
+      <c r="F54" s="9">
+        <v>151.1</v>
+      </c>
+      <c r="G54" s="9">
+        <v>133</v>
+      </c>
+      <c r="H54" s="9">
+        <v>121.8</v>
+      </c>
+      <c r="I54" s="9">
+        <v>117.8</v>
+      </c>
+    </row>
+    <row r="55" s="1" customFormat="1" ht="14.9324" customHeight="1">
+      <c r="B55" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C55" s="10">
         <v>122.8</v>
       </c>
-      <c r="D54" s="10">
+      <c r="D55" s="10">
         <v>117.5</v>
       </c>
-      <c r="E54" s="10">
+      <c r="E55" s="10">
         <v>109.8</v>
       </c>
-      <c r="F54" s="10">
+      <c r="F55" s="10">
         <v>142.9</v>
       </c>
-      <c r="G54" s="10">
+      <c r="G55" s="10">
         <v>121.3</v>
       </c>
-      <c r="H54" s="10">
+      <c r="H55" s="10">
         <v>127.7</v>
       </c>
-      <c r="I54" s="10">
+      <c r="I55" s="10">
         <v>110</v>
       </c>
     </row>
-    <row r="55" s="1" customFormat="1" ht="14.9324" customHeight="1">
-      <c r="B55" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="C55" s="12">
+    <row r="56" s="1" customFormat="1" ht="14.9324" customHeight="1">
+      <c r="B56" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="C56" s="13">
         <v>111.1</v>
       </c>
-      <c r="D55" s="12">
+      <c r="D56" s="13">
         <v>108.5</v>
       </c>
-      <c r="E55" s="12">
+      <c r="E56" s="13">
         <v>103.2</v>
       </c>
-      <c r="F55" s="12">
+      <c r="F56" s="13">
         <v>117.2</v>
       </c>
-      <c r="G55" s="12">
+      <c r="G56" s="13">
         <v>108.8</v>
       </c>
-      <c r="H55" s="12">
+      <c r="H56" s="13">
         <v>119.3</v>
       </c>
-      <c r="I55" s="12">
+      <c r="I56" s="13">
         <v>105.9</v>
       </c>
     </row>
-    <row r="56" s="1" customFormat="1" ht="25.0651" customHeight="1"/>
-    <row r="57" s="1" customFormat="1" ht="81.0616" customHeight="1">
-      <c r="B57" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="C57" s="16"/>
-      <c r="D57" s="16"/>
-      <c r="E57" s="16"/>
-      <c r="F57" s="16"/>
-      <c r="G57" s="16"/>
-      <c r="H57" s="16"/>
-      <c r="I57" s="16"/>
-      <c r="J57" s="16"/>
-      <c r="K57" s="16"/>
-      <c r="L57" s="16"/>
-    </row>
+    <row r="57" s="1" customFormat="1" ht="25.0651" customHeight="1"/>
+    <row r="58" s="1" customFormat="1" ht="81.0616" customHeight="1">
+      <c r="B58" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="C58" s="17"/>
+      <c r="D58" s="17"/>
+      <c r="E58" s="17"/>
+      <c r="F58" s="17"/>
+      <c r="G58" s="17"/>
+      <c r="H58" s="17"/>
+      <c r="I58" s="17"/>
+      <c r="J58" s="17"/>
+      <c r="K58" s="17"/>
+      <c r="L58" s="17"/>
+    </row>
+    <row r="59" s="1" customFormat="1" ht="28.7982" customHeight="1"/>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B42:D42"/>
     <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B57:L57"/>
-    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="B58:L58"/>
+    <mergeCell ref="D24:E24"/>
     <mergeCell ref="D4:E4"/>
-    <mergeCell ref="D40:E40"/>
+    <mergeCell ref="D41:E41"/>
   </mergeCells>
   <pageSetup paperSize="9" scale="100" orientation="landscape"/>
   <headerFooter alignWithMargins="0"/>
